--- a/test_code/station_data.xlsx
+++ b/test_code/station_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,19 +510,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.53</v>
+        <v>75.59399999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>288.19</v>
+        <v>248.002</v>
       </c>
       <c r="D2" t="n">
-        <v>101.401</v>
+        <v>30.355</v>
       </c>
       <c r="E2" t="n">
-        <v>288.544</v>
+        <v>248.249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.53</v>
+        <v>234.095</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -531,27 +531,25 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="J2" t="n">
-        <v>288.19</v>
+        <v>216.595</v>
       </c>
       <c r="K2" t="n">
-        <v>289.15</v>
+        <v>217.069</v>
       </c>
       <c r="L2" t="n">
-        <v>101.401</v>
+        <v>18.92</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>250.9</v>
       </c>
       <c r="N2" t="n">
-        <v>1.226</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.304</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="3">
@@ -559,19 +557,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.53</v>
+        <v>75.59399999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>288.19</v>
+        <v>248.002</v>
       </c>
       <c r="D3" t="n">
-        <v>101.401</v>
+        <v>30.355</v>
       </c>
       <c r="E3" t="n">
-        <v>288.544</v>
+        <v>248.249</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>234.095</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -580,45 +578,45 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J3" t="n">
-        <v>287.614</v>
+        <v>231.291</v>
       </c>
       <c r="K3" t="n">
-        <v>288.572</v>
+        <v>231.797</v>
       </c>
       <c r="L3" t="n">
-        <v>100.694</v>
+        <v>23.793</v>
       </c>
       <c r="M3" t="n">
-        <v>34.007</v>
+        <v>183.016</v>
       </c>
       <c r="N3" t="n">
-        <v>1.22</v>
+        <v>0.358</v>
       </c>
       <c r="O3" t="n">
-        <v>0.013</v>
+        <v>1.153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.53</v>
+        <v>55.959</v>
       </c>
       <c r="C4" t="n">
-        <v>288.19</v>
+        <v>248.002</v>
       </c>
       <c r="D4" t="n">
-        <v>99.373</v>
+        <v>30.355</v>
       </c>
       <c r="E4" t="n">
-        <v>288.544</v>
+        <v>248.249</v>
       </c>
       <c r="F4" t="n">
-        <v>0.54</v>
+        <v>173.291</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -627,45 +625,45 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="J4" t="n">
-        <v>283.085</v>
+        <v>233.807</v>
       </c>
       <c r="K4" t="n">
-        <v>284.028</v>
+        <v>234.319</v>
       </c>
       <c r="L4" t="n">
-        <v>93.355</v>
+        <v>24.709</v>
       </c>
       <c r="M4" t="n">
-        <v>101.214</v>
+        <v>168.675</v>
       </c>
       <c r="N4" t="n">
-        <v>1.149</v>
+        <v>0.368</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.53</v>
+        <v>55.959</v>
       </c>
       <c r="C5" t="n">
-        <v>431.098</v>
+        <v>328.861</v>
       </c>
       <c r="D5" t="n">
-        <v>357.742</v>
+        <v>75.887</v>
       </c>
       <c r="E5" t="n">
-        <v>432.741</v>
+        <v>329.395</v>
       </c>
       <c r="F5" t="n">
-        <v>0.184</v>
+        <v>79.821</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -674,45 +672,45 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>0.474</v>
       </c>
       <c r="J5" t="n">
-        <v>417.955</v>
+        <v>314.747</v>
       </c>
       <c r="K5" t="n">
-        <v>425.198</v>
+        <v>324.895</v>
       </c>
       <c r="L5" t="n">
-        <v>320.565</v>
+        <v>65.07599999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>163.527</v>
+        <v>168.494</v>
       </c>
       <c r="N5" t="n">
-        <v>2.672</v>
+        <v>0.72</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3.07</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>0.53</v>
+        <v>19.635</v>
       </c>
       <c r="C6" t="n">
-        <v>809.418</v>
+        <v>248.002</v>
       </c>
       <c r="D6" t="n">
-        <v>336.278</v>
+        <v>30.355</v>
       </c>
       <c r="E6" t="n">
-        <v>832.455</v>
+        <v>248.249</v>
       </c>
       <c r="F6" t="n">
-        <v>0.268</v>
+        <v>60.804</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -721,260 +719,354 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="J6" t="n">
-        <v>803.746</v>
+        <v>233.807</v>
       </c>
       <c r="K6" t="n">
-        <v>884.619</v>
+        <v>234.319</v>
       </c>
       <c r="L6" t="n">
-        <v>327.332</v>
+        <v>24.709</v>
       </c>
       <c r="M6" t="n">
-        <v>111.735</v>
+        <v>168.675</v>
       </c>
       <c r="N6" t="n">
-        <v>1.419</v>
+        <v>0.368</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="B7" t="n">
-        <v>0.541</v>
+        <v>19.635</v>
       </c>
       <c r="C7" t="n">
-        <v>1510</v>
+        <v>328.861</v>
       </c>
       <c r="D7" t="n">
-        <v>319.464</v>
+        <v>75.887</v>
       </c>
       <c r="E7" t="n">
-        <v>1692.591</v>
+        <v>329.395</v>
       </c>
       <c r="F7" t="n">
-        <v>0.393</v>
+        <v>28.007</v>
       </c>
       <c r="G7" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1475.134</v>
+        <v>323.055</v>
       </c>
       <c r="K7" t="n">
-        <v>1856.639</v>
+        <v>324.895</v>
       </c>
       <c r="L7" t="n">
-        <v>288.361</v>
+        <v>71.29600000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>296.254</v>
+        <v>108.072</v>
       </c>
       <c r="N7" t="n">
-        <v>0.681</v>
+        <v>0.769</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6.07</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>0.541</v>
+        <v>19.046</v>
       </c>
       <c r="C8" t="n">
-        <v>1391.582</v>
+        <v>631.349</v>
       </c>
       <c r="D8" t="n">
-        <v>219.139</v>
+        <v>607.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1545.18</v>
+        <v>640.251</v>
       </c>
       <c r="F8" t="n">
-        <v>0.55</v>
+        <v>4.705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1354.077</v>
+        <v>620.9450000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1686.05</v>
+        <v>656.965</v>
       </c>
       <c r="L8" t="n">
-        <v>194.648</v>
+        <v>571.035</v>
       </c>
       <c r="M8" t="n">
-        <v>305.614</v>
+        <v>148.373</v>
       </c>
       <c r="N8" t="n">
-        <v>0.501</v>
+        <v>3.204</v>
       </c>
       <c r="O8" t="n">
-        <v>0.004</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.08</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>0.541</v>
+        <v>19.532</v>
       </c>
       <c r="C9" t="n">
-        <v>1064.071</v>
+        <v>1510</v>
       </c>
       <c r="D9" t="n">
-        <v>205.991</v>
+        <v>576.745</v>
       </c>
       <c r="E9" t="n">
-        <v>1145.406</v>
+        <v>1702.769</v>
       </c>
       <c r="F9" t="n">
-        <v>0.511</v>
+        <v>7.855</v>
       </c>
       <c r="G9" t="n">
-        <v>0.011</v>
+        <v>0.474</v>
       </c>
       <c r="H9" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1049.105</v>
+        <v>1456.786</v>
       </c>
       <c r="K9" t="n">
-        <v>1251.123</v>
+        <v>1849.14</v>
       </c>
       <c r="L9" t="n">
-        <v>194.219</v>
+        <v>492.134</v>
       </c>
       <c r="M9" t="n">
-        <v>188.931</v>
+        <v>367.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0.645</v>
+        <v>1.177</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="B10" t="n">
-        <v>0.552</v>
+        <v>19.562</v>
       </c>
       <c r="C10" t="n">
-        <v>1700</v>
+        <v>1234.609</v>
       </c>
       <c r="D10" t="n">
-        <v>205.991</v>
+        <v>225.913</v>
       </c>
       <c r="E10" t="n">
-        <v>1933.656</v>
+        <v>1359.022</v>
       </c>
       <c r="F10" t="n">
-        <v>0.659</v>
+        <v>18.161</v>
       </c>
       <c r="G10" t="n">
-        <v>0.011</v>
+        <v>0.486</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="I10" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="J10" t="n">
-        <v>1638.312</v>
+        <v>1197.792</v>
       </c>
       <c r="K10" t="n">
-        <v>2093.834</v>
+        <v>1476.377</v>
       </c>
       <c r="L10" t="n">
-        <v>174.734</v>
+        <v>198.373</v>
       </c>
       <c r="M10" t="n">
-        <v>397.09</v>
+        <v>301.267</v>
       </c>
       <c r="N10" t="n">
-        <v>0.372</v>
+        <v>0.577</v>
       </c>
       <c r="O10" t="n">
-        <v>0.004</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>19.562</v>
+      </c>
+      <c r="C11" t="n">
+        <v>971.611</v>
+      </c>
+      <c r="D11" t="n">
+        <v>76.506</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1041.844</v>
+      </c>
+      <c r="F11" t="n">
+        <v>47.574</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>934.212</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1105.495</v>
+      </c>
+      <c r="L11" t="n">
+        <v>65.07599999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>297.51</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.271</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75.521</v>
+      </c>
+      <c r="C12" t="n">
+        <v>495.352</v>
+      </c>
+      <c r="D12" t="n">
+        <v>75.248</v>
+      </c>
+      <c r="E12" t="n">
+        <v>500.666</v>
+      </c>
+      <c r="F12" t="n">
+        <v>133.333</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="J12" t="n">
+        <v>471.685</v>
+      </c>
+      <c r="K12" t="n">
+        <v>489.085</v>
+      </c>
+      <c r="L12" t="n">
+        <v>63.052</v>
+      </c>
+      <c r="M12" t="n">
+        <v>221.537</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.732</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>8</v>
       </c>
-      <c r="B11" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1700</v>
-      </c>
-      <c r="D11" t="n">
-        <v>205.991</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1933.656</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="B13" t="n">
+        <v>75.521</v>
+      </c>
+      <c r="C13" t="n">
+        <v>495.352</v>
+      </c>
+      <c r="D13" t="n">
+        <v>75.248</v>
+      </c>
+      <c r="E13" t="n">
+        <v>500.666</v>
+      </c>
+      <c r="F13" t="n">
+        <v>133.333</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
-        <v>1484.938</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1897.815</v>
-      </c>
-      <c r="L11" t="n">
-        <v>112.801</v>
-      </c>
-      <c r="M11" t="n">
-        <v>741.4299999999999</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.003</v>
+      <c r="J13" t="n">
+        <v>415.77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>431.107</v>
+      </c>
+      <c r="L13" t="n">
+        <v>39.971</v>
+      </c>
+      <c r="M13" t="n">
+        <v>406.244</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.555</v>
       </c>
     </row>
   </sheetData>
